--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104483_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104483_W3.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3118</v>
+        <v>3.8252</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3124</v>
+        <v>2.5025</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9994</v>
+        <v>1.3227</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1644</v>
+        <v>1.142</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9801</v>
+        <v>1.9599</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8157</v>
+        <v>-0.8179</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6773</v>
+        <v>2.6295</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6108</v>
+        <v>2.5781</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.513</v>
+        <v>-1.4876</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R2" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4484</v>
+        <v>-0.9119</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5353</v>
+        <v>-0.2769</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9131</v>
+        <v>-0.635</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4617</v>
+        <v>2.457</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8067</v>
+        <v>2.197</v>
       </c>
       <c r="E3" t="n">
-        <v>3.903</v>
+        <v>3.3032</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0964</v>
+        <v>-1.1062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.344</v>
+        <v>0.3518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2294</v>
+        <v>0.2325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J3" t="n">
-        <v>0.698</v>
+        <v>0.695</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.354</v>
+        <v>-0.3432</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9409</v>
+        <v>0.3216</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0858</v>
+        <v>0.4991</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3916</v>
+        <v>-0.7466</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5595</v>
+        <v>-0.6957</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1679</v>
+        <v>-0.051</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4962</v>
+        <v>0.4886</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4028</v>
+        <v>0.3885</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7833</v>
+        <v>0.7592</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6714</v>
+        <v>0.6475</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2871</v>
+        <v>-0.2706</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3057</v>
+        <v>0.1729</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6816</v>
+        <v>0.4572</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3759</v>
+        <v>-0.2843</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5246</v>
+        <v>-1.1547</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2335</v>
+        <v>-0.7733</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2911</v>
+        <v>-0.3814</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9633</v>
+        <v>-0.957</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0705</v>
+        <v>1.0794</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0338</v>
+        <v>-2.0364</v>
       </c>
       <c r="J5" t="n">
-        <v>0.856</v>
+        <v>0.8304</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5758</v>
+        <v>1.5686</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8193</v>
+        <v>-1.7874</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9757</v>
+        <v>-0.6108</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1179</v>
+        <v>0.3782</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8578</v>
+        <v>-0.989</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7198</v>
+        <v>-0.7251</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6657</v>
+        <v>-1.9808</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0011</v>
+        <v>-1.3228</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6646</v>
+        <v>-0.658</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3749</v>
+        <v>0.356</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3304</v>
+        <v>-1.5816</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0444</v>
+        <v>1.9376</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6696</v>
+        <v>1.286</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0795</v>
+        <v>-1.1936</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.749</v>
+        <v>2.4795</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7053</v>
+        <v>-0.93</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4099</v>
+        <v>-0.3881</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2954</v>
+        <v>-0.5419</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3648</v>
+        <v>-0.3172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8953</v>
+        <v>-0.1048</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5305</v>
+        <v>-0.2124</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1093</v>
+        <v>-1.792</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1093</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7092</v>
+        <v>-2.5828</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8673</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8419</v>
+        <v>-1.8373</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3804</v>
+        <v>-2.3693</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5653</v>
+        <v>-0.3303</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9458</v>
+        <v>-2.039</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3235</v>
+        <v>-0.6802</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1713</v>
+        <v>0.0722</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4948</v>
+        <v>-0.7524</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9431</v>
+        <v>-1.6891</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.394</v>
+        <v>-0.4025</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.549</v>
+        <v>-1.2866</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0631</v>
+        <v>-0.5598</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>0.1623</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3675</v>
+        <v>-0.7221</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7997</v>
+        <v>-0.1089</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7997</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8223</v>
+        <v>-2.7814</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.398</v>
+        <v>-4.1994</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5757</v>
+        <v>1.418</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9088</v>
+        <v>-1.9166</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0345</v>
+        <v>-1.0421</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8743</v>
+        <v>-0.8744</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.8868</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5928</v>
+        <v>-0.6108</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2226</v>
+        <v>0.2717</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0907</v>
+        <v>0.3295</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1318</v>
+        <v>-0.0578</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9557</v>
+        <v>-2.8978</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3063</v>
+        <v>-1.6171</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6494</v>
+        <v>-1.2808</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0268</v>
+        <v>-3.1106</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.1612</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2794</v>
+        <v>-2.9494</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1056</v>
+        <v>-1.3637</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1803</v>
+        <v>0.9308</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>-2.2945</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9212</v>
+        <v>-1.7469</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5672</v>
+        <v>-1.092</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.354</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.366</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1603</v>
+        <v>-0.2047</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5263</v>
+        <v>-0.4248</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1093</v>
+        <v>0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1093</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.58</v>
+        <v>-3.1626</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2074</v>
+        <v>-1.5313</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3726</v>
+        <v>-1.6314</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1182</v>
+        <v>-2.0155</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1675</v>
+        <v>-0.7468</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9507</v>
+        <v>-1.2687</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3493</v>
+        <v>-0.1119</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9351</v>
+        <v>-0.1864</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2844</v>
+        <v>0.0745</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7689</v>
+        <v>-1.9036</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1026</v>
+        <v>-0.5604</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6663</v>
+        <v>-1.3432</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3011</v>
+        <v>-0.583</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8166</v>
+        <v>-0.0536</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4845</v>
+        <v>-0.5294</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>-0.1089</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7425</v>
+        <v>-3.3213</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.111</v>
+        <v>-1.6549</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6315</v>
+        <v>-1.6663</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1303</v>
+        <v>1.1373</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1462</v>
+        <v>1.1517</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7139</v>
+        <v>0.7052</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4165</v>
+        <v>0.432</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8462</v>
+        <v>-0.4389</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2898</v>
+        <v>-0.3551</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8281</v>
+        <v>-3.4971</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0257</v>
+        <v>-3.5049</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1976</v>
+        <v>0.0078</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6654</v>
+        <v>-1.6576</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4069</v>
+        <v>-1.4046</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2585</v>
+        <v>-0.253</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8747</v>
+        <v>-0.8843</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.7733</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.244</v>
+        <v>-1.2355</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3215</v>
+        <v>0.0011</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8166</v>
+        <v>-0.2744</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4951</v>
+        <v>0.2755</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5666</v>
+        <v>-4.7376</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0837</v>
+        <v>-2.4948</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4829</v>
+        <v>-2.2428</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1214</v>
+        <v>-2.1211</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1081</v>
+        <v>-2.1108</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0133</v>
+        <v>-0.0103</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0452</v>
+        <v>-1.0637</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.0127</v>
+        <v>-2.0242</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0762</v>
+        <v>-1.0574</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5627</v>
+        <v>-0.7352</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6775</v>
+        <v>-0.0653</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8853</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.8846</v>
+        <v>-20.8405</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.4591</v>
+        <v>-12.734</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.425599999999999</v>
+        <v>-8.1067</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.6635</v>
+        <v>-10.672</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.6933</v>
+        <v>-3.7315</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.9701</v>
+        <v>-6.940300000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>2.148200000000001</v>
+        <v>1.9147</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4554</v>
+        <v>2.305799999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3071000000000004</v>
+        <v>-0.3910999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.8118</v>
+        <v>-12.5869</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.1488</v>
+        <v>-6.0375</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.663</v>
+        <v>-6.5492</v>
       </c>
       <c r="P14" t="n">
-        <v>9.999999999965592e-05</v>
+        <v>0.0001000000000003221</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.415</v>
+        <v>-20.4868</v>
       </c>
       <c r="R14" t="n">
-        <v>20.4149</v>
+        <v>20.4867</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.050699999999999</v>
+        <v>-4.019</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3023000000000002</v>
+        <v>0.7627999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.748699999999999</v>
+        <v>-4.7818</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.1705</v>
+        <v>-6.1496</v>
       </c>
       <c r="W14" t="n">
-        <v>5.110200000000001</v>
+        <v>5.075299999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.2806</v>
+        <v>-11.225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8816</v>
+        <v>6.0852</v>
       </c>
       <c r="E15" t="n">
-        <v>6.127</v>
+        <v>4.4641</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7546</v>
+        <v>1.6211</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6328</v>
+        <v>5.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0593</v>
+        <v>2.8776</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6921</v>
+        <v>2.1225</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4521</v>
+        <v>5.0836</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9973</v>
+        <v>3.0509</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4548</v>
+        <v>2.0327</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8193</v>
+        <v>-0.0835</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0566</v>
+        <v>-0.1733</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2373</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8147</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5168</v>
+        <v>0.0849</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2362</v>
+        <v>-0.0653</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2806</v>
+        <v>0.1503</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0515</v>
+        <v>1.683</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.9497</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2019</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3112</v>
+        <v>5.2996</v>
       </c>
       <c r="E16" t="n">
-        <v>4.039</v>
+        <v>4.4395</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2721</v>
+        <v>0.8601</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0014</v>
+        <v>2.633</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8743</v>
+        <v>-0.0494</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1271</v>
+        <v>2.6824</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1121</v>
+        <v>3.4204</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0651</v>
+        <v>0.9858</v>
       </c>
       <c r="L16" t="n">
-        <v>2.047</v>
+        <v>2.4346</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1107</v>
+        <v>-0.7874</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1908</v>
+        <v>-1.0351</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>0.2477</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-1.8211</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7002</v>
+        <v>1.9349</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5383</v>
+        <v>1.5929</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1618</v>
+        <v>0.3419</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6905</v>
+        <v>0.0488</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9604</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.27</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2436</v>
+        <v>4.2072</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3665</v>
+        <v>2.1062</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8771</v>
+        <v>2.101</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0421</v>
+        <v>4.0501</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8613</v>
+        <v>2.8688</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1808</v>
+        <v>1.1813</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0224</v>
+        <v>4.0033</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2339</v>
+        <v>2.2236</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7885</v>
+        <v>1.7797</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0197</v>
+        <v>0.0468</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0502</v>
+        <v>-0.0997</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.141</v>
+        <v>0.0446</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5929</v>
+        <v>3.7199</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7347</v>
+        <v>0.5903</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8582</v>
+        <v>3.1296</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8405</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4257</v>
+        <v>-1.4246</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2789</v>
+        <v>2.2651</v>
       </c>
       <c r="J18" t="n">
-        <v>0.205</v>
+        <v>0.1796</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7085</v>
+        <v>1.6899</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6483</v>
+        <v>0.6609</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4467</v>
+        <v>0.5819</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5958</v>
+        <v>0.4806</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1491</v>
+        <v>0.1013</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.004</v>
+        <v>3.0545</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7584</v>
+        <v>2.8177</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2455</v>
+        <v>0.2368</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7938</v>
+        <v>0.793</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4241</v>
+        <v>0.5516</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3697</v>
+        <v>0.2414</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0799</v>
+        <v>1.4937</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9453</v>
+        <v>0.8683</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1346</v>
+        <v>0.6254</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2861</v>
+        <v>-0.7007</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5212</v>
+        <v>-0.3168</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7649</v>
+        <v>-0.384</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1854</v>
+        <v>0.855</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6261</v>
+        <v>0.7385</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4406</v>
+        <v>0.1165</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5297</v>
+        <v>1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7997</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.27</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2407</v>
+        <v>2.9002</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9068</v>
+        <v>2.8411</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3339</v>
+        <v>0.0591</v>
       </c>
       <c r="G20" t="n">
-        <v>0.794</v>
+        <v>2.802</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5541</v>
+        <v>0.4305</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2399</v>
+        <v>2.3716</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5179</v>
+        <v>4.0619</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8863</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6317</v>
+        <v>3.1279</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7239</v>
+        <v>-1.2599</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3321</v>
+        <v>-0.5036</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.7563</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0345</v>
+        <v>-0.2889</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>-0.5089</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2431</v>
+        <v>0.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.639</v>
+        <v>1.5253</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1853</v>
+        <v>1.792</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5463</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0689</v>
+        <v>2.0033</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.312</v>
+        <v>-0.3453</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3809</v>
+        <v>2.3486</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4713</v>
+        <v>0.4653</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1124</v>
+        <v>-0.1202</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5838</v>
+        <v>0.5855</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3026</v>
+        <v>0.2766</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1425</v>
+        <v>-0.1626</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1688</v>
+        <v>0.1887</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.48</v>
+        <v>0.4193</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0393</v>
+        <v>0.0414</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4406</v>
+        <v>0.3779</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4371</v>
+        <v>0.4358</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6748</v>
+        <v>0.437</v>
       </c>
       <c r="E22" t="n">
-        <v>0.175</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4999</v>
+        <v>0.3388</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1627</v>
+        <v>-0.6334</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4877</v>
+        <v>-1.2266</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6504</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4027</v>
+        <v>-0.5773</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3463</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.749</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>0.24</v>
+        <v>-0.0562</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1414</v>
+        <v>-0.5749</v>
       </c>
       <c r="O22" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5692</v>
+        <v>0.6363</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5777</v>
+        <v>0.7453</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.1089</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1555</v>
+        <v>0.2668</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2522</v>
+        <v>-0.1825</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.4493</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6444</v>
+        <v>-0.1628</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2309</v>
+        <v>0.4882</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5865</v>
+        <v>-0.651</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5732</v>
+        <v>-0.4077</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6478</v>
+        <v>0.3447</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0746</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0712</v>
+        <v>0.2449</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5831</v>
+        <v>0.1435</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5118</v>
+        <v>0.1014</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0599</v>
+        <v>0.1533</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3871</v>
+        <v>0.2252</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3273</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4027</v>
+        <v>-1.0534</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7513</v>
+        <v>-1.9901</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3486</v>
+        <v>0.9368</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5349</v>
+        <v>-1.3244</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4633</v>
+        <v>-0.0494</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0716</v>
+        <v>-1.275</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2159</v>
+        <v>-0.7379</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.163</v>
+        <v>0.0517</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.053</v>
+        <v>-0.7896</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3189</v>
+        <v>-0.5865</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3003</v>
+        <v>-0.1011</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0186</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.9903</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5081</v>
+        <v>-0.5029</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0162</v>
+        <v>-0.1141</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5081</v>
+        <v>-0.3888</v>
       </c>
       <c r="V24" t="n">
-        <v>2.3461</v>
+        <v>0.7739</v>
       </c>
       <c r="W24" t="n">
-        <v>3.4387</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6086</v>
+        <v>-1.2231</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3373</v>
+        <v>-1.9132</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7288</v>
+        <v>0.6902</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.3361</v>
+        <v>-1.5342</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0593</v>
+        <v>-0.457</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2768</v>
+        <v>-1.0772</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-1.2348</v>
       </c>
       <c r="K25" t="n">
-        <v>0.052</v>
+        <v>-0.1691</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7864</v>
+        <v>-1.0656</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6017</v>
+        <v>-0.2995</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1113</v>
+        <v>-0.2879</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4904</v>
+        <v>-0.0116</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-5.0079</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0437</v>
+        <v>0.706</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4688</v>
+        <v>0.9032</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.575</v>
+        <v>-0.1972</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7712</v>
+        <v>2.3367</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.4262</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7712</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9662</v>
+        <v>-3.0214</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.0288</v>
+        <v>-4.8191</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0626</v>
+        <v>1.7977</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0899</v>
+        <v>-2.0993</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.954</v>
+        <v>-2.9747</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.0335</v>
+        <v>-3.0469</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4151</v>
+        <v>1.374</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6472</v>
+        <v>0.8871</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7679</v>
+        <v>0.4868</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>21.8847</v>
+        <v>22.6758</v>
       </c>
       <c r="E27" t="n">
-        <v>8.425800000000002</v>
+        <v>8.1068</v>
       </c>
       <c r="F27" t="n">
-        <v>13.4589</v>
+        <v>14.5691</v>
       </c>
       <c r="G27" t="n">
-        <v>10.6635</v>
+        <v>10.672</v>
       </c>
       <c r="H27" t="n">
-        <v>3.693300000000001</v>
+        <v>3.7316</v>
       </c>
       <c r="I27" t="n">
-        <v>6.9701</v>
+        <v>6.940500000000002</v>
       </c>
       <c r="J27" t="n">
-        <v>12.81179999999999</v>
+        <v>12.5867</v>
       </c>
       <c r="K27" t="n">
-        <v>6.149</v>
+        <v>6.037500000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6629</v>
+        <v>6.549399999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.1481</v>
+        <v>-1.915</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.4555</v>
+        <v>-2.306</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3070999999999999</v>
+        <v>0.3910000000000002</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>-20.415</v>
+        <v>-20.4868</v>
       </c>
       <c r="R27" t="n">
-        <v>20.415</v>
+        <v>20.4869</v>
       </c>
       <c r="S27" t="n">
-        <v>5.050799999999999</v>
+        <v>5.854099999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>4.7483</v>
+        <v>4.7816</v>
       </c>
       <c r="U27" t="n">
-        <v>0.302</v>
+        <v>1.0725</v>
       </c>
       <c r="V27" t="n">
-        <v>6.170500000000001</v>
+        <v>6.149800000000002</v>
       </c>
       <c r="W27" t="n">
-        <v>11.2804</v>
+        <v>11.2251</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.110199999999999</v>
+        <v>-5.075299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104483_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104483_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.225</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104483_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-5.075299999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
